--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,10 +2649,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130766037</v>
+        <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>58167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,26 +2660,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2689,21 +2689,17 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Transätter Gullsätra, Transätter Gullsätra, Flen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587329</v>
+        <v>587343</v>
       </c>
       <c r="R18" t="n">
-        <v>6550354</v>
+        <v>6550351</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2730,27 +2726,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Vid fågelmatning</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2776,43 +2767,43 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130766037</t>
+          <t>https://artportalen.se/Sighting/137220381</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132437408</v>
+        <v>130766037</v>
       </c>
       <c r="B19" t="n">
-        <v>58375</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103037</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2822,17 +2813,21 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Transätter Gullsätra, Transätter Gullsätra, Flen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R19" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2859,22 +2854,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Vid fågelmatning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2900,33 +2900,33 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132437408</t>
+          <t>https://artportalen.se/Sighting/130766037</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132437413</v>
+        <v>132437408</v>
       </c>
       <c r="B20" t="n">
-        <v>58596</v>
+        <v>58375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3024,51 +3024,47 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132437413</t>
+          <t>https://artportalen.se/Sighting/132437408</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132437415</v>
+        <v>132437413</v>
       </c>
       <c r="B21" t="n">
-        <v>58624</v>
+        <v>58596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3116,7 +3112,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3126,7 +3122,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3152,16 +3148,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132437415</t>
+          <t>https://artportalen.se/Sighting/132437413</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134916688</v>
+        <v>132437415</v>
       </c>
       <c r="B22" t="n">
-        <v>58629</v>
+        <v>58624</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3192,7 +3188,11 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587329</v>
+        <v>587343</v>
       </c>
       <c r="R22" t="n">
-        <v>6550354</v>
+        <v>6550351</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3235,22 +3235,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,33 +3276,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134916688</t>
+          <t>https://artportalen.se/Sighting/132437415</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131718548</v>
+        <v>134916688</v>
       </c>
       <c r="B23" t="n">
-        <v>58658</v>
+        <v>58629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R23" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3359,22 +3359,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3400,48 +3400,52 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131718548</t>
+          <t>https://artportalen.se/Sighting/134916688</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501882</v>
+        <v>131718548</v>
       </c>
       <c r="B24" t="n">
-        <v>58676</v>
+        <v>58658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3479,22 +3483,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3520,33 +3524,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131501882</t>
+          <t>https://artportalen.se/Sighting/131718548</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131393404</v>
+        <v>131501882</v>
       </c>
       <c r="B25" t="n">
-        <v>58085</v>
+        <v>58676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3556,16 +3560,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587329</v>
+        <v>587343</v>
       </c>
       <c r="R25" t="n">
-        <v>6550354</v>
+        <v>6550351</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3603,22 +3603,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3644,16 +3644,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131393404</t>
+          <t>https://artportalen.se/Sighting/131501882</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133893870</v>
+        <v>131393404</v>
       </c>
       <c r="B26" t="n">
-        <v>58107</v>
+        <v>58085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3678,10 +3678,18 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3689,10 +3697,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587343</v>
+        <v>587329</v>
       </c>
       <c r="R26" t="n">
-        <v>6550351</v>
+        <v>6550354</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3719,22 +3727,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3759,6 +3767,122 @@
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131393404</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133893870</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Transätter Gullsätra, Transätter Gullsätra, Flen, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>587343</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6550351</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Leif Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Leif Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133893870</t>
         </is>
@@ -3791,6 +3915,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2684,11 +2684,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4724-2024 artfynd.xlsx
+++ b/artfynd/A 4724-2024 artfynd.xlsx
@@ -2652,7 +2652,7 @@
         <v>137220381</v>
       </c>
       <c r="B18" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
